--- a/artfynd/A 63112-2020 artfynd.xlsx
+++ b/artfynd/A 63112-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688275</v>
       </c>
       <c r="B2" t="n">
-        <v>92177</v>
+        <v>92182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 63112-2020 artfynd.xlsx
+++ b/artfynd/A 63112-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688275</v>
       </c>
       <c r="B2" t="n">
-        <v>92182</v>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 63112-2020 artfynd.xlsx
+++ b/artfynd/A 63112-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688275</v>
       </c>
       <c r="B2" t="n">
-        <v>92183</v>
+        <v>92188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 63112-2020 artfynd.xlsx
+++ b/artfynd/A 63112-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688275</v>
       </c>
       <c r="B2" t="n">
-        <v>92188</v>
+        <v>92192</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
